--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103211</v>
+        <v>103221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103221</v>
+        <v>103234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103234</v>
+        <v>103235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103235</v>
+        <v>103238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103238</v>
+        <v>103244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>103244</v>
+        <v>103245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104013</v>
+        <v>104016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104016</v>
+        <v>104042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104042</v>
+        <v>104043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104043</v>
+        <v>104044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104044</v>
+        <v>104046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104046</v>
+        <v>104050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104050</v>
+        <v>104063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104063</v>
+        <v>104064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104064</v>
+        <v>104067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104067</v>
+        <v>104081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104081</v>
+        <v>104101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>121232938</v>
       </c>
       <c r="B4" t="n">
-        <v>104101</v>
+        <v>104115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20975-2024 artfynd.xlsx
+++ b/artfynd/A 20975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116495173</v>
+        <v>114777376</v>
       </c>
       <c r="B2" t="n">
-        <v>94183</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Elisetorpslunden (Elisetorpslunden), Sk</t>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410842</v>
+        <v>410938</v>
       </c>
       <c r="R2" t="n">
-        <v>6200961</v>
+        <v>6200975</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116796812</v>
+        <v>116495173</v>
       </c>
       <c r="B3" t="n">
-        <v>94189</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +814,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Elisetorpslunden (Elisetorpslunden), Sk</t>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410827</v>
+        <v>410842</v>
       </c>
       <c r="R3" t="n">
-        <v>6200960</v>
+        <v>6200961</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,22 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121232938</v>
+        <v>116796812</v>
       </c>
       <c r="B4" t="n">
-        <v>104115</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +901,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222395</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>300 m SV Elisetorp, Sk</t>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410958</v>
+        <v>410827</v>
       </c>
       <c r="R4" t="n">
-        <v>6201069</v>
+        <v>6200960</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,12 +955,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,34 +981,344 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>längs skogsbäck</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>H144</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116796664</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101974</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410822</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6200976</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121232937</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>300 m SV Elisetorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>410958</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6201069</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>längs skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121232938</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104252</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>300 m SV Elisetorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>410958</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6201069</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>längs skogsbäck</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>H144</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
